--- a/docassemble/MAEvictionDefense/data/sources/eviction_ht.xlsx
+++ b/docassemble/MAEvictionDefense/data/sources/eviction_ht.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1221"/>
+  <dimension ref="A1:H1225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.7109375" customWidth="1" min="1" max="1"/>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>06affba7ad2203d850a91c6af6819f61</t>
+          <t>575ad08957cfe9bd85d7f94d8711ed35</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -18207,7 +18207,7 @@
           <t xml:space="preserve">You can continue this interview on another device, or share it with 
 someone who will help you finish it. Choose any of the options below to share
 the interview.
-Right-click and copy [this link](${interview_url()}).
+Right-click and copy [the link to your interview](${interview_url()}).
 % if device() and not device().is_mobile:
 Use your phone's camera to point at this barcode. Click the link that appears
 in the camera's viewfinder.
@@ -18223,7 +18223,7 @@
           <t>Ou ka kontinye entèvyou sa a sou yon lòt aparèy, oswa pataje li avèk yo
 yon moun ki pral ede ou fini li. Chwazi nenpòt nan opsyon ki anba a yo pataje
 entèvyou a.
-Fè klik dwat epi kopye [this link](${interview_url()}).
+Fè klik dwat epi kopye [lyen entèvyou w la](${interview_url()}).
 % if device() and not device().is_mobile:
 Itilize kamera telefòn ou an pou pwente l vè kòdaba sa a. Klike sou lyen ki parèt nan ekran kamera a sou telefòn ou. 
 &lt;center&gt;
@@ -40410,7 +40410,7 @@
       </c>
       <c r="D949" s="2" t="inlineStr">
         <is>
-          <t>405a7c1de4db0b51f49baacb5de85580</t>
+          <t>8d80904edef43f2eedc35a288289b349</t>
         </is>
       </c>
       <c r="E949" s="2" t="inlineStr">
@@ -40440,7 +40440,7 @@
   ${landlord.name}.
 % endif
 You also need to send a copy of the motion to ${court}.
-Learn more and continue the form online [here](${interview_url()}) or download
+Learn more and [continue the form online](${interview_url()}) or download
 the PDF here: https://gbls.org/tactics/compel.
 </t>
         </is>
@@ -40461,7 +40461,7 @@
   ${landlord.name}.
 % endif
 Anplis sa, ou bezwen voye yon kopi mosyon an bay ${court}.
-Aprann plis epi kontinye fòmilè a anlin [isit](${interview_url()}) oswa telechaje
+Aprann plis epi [kontinye fòmilè a anlin](${interview_url()}) oswa telechaje
 PDF la isit : https://gbls.org/tactics/compel.
 </t>
         </is>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="D955" s="2" t="inlineStr">
         <is>
-          <t>26fd8aed4ec30f78c45f916032146cd5</t>
+          <t>cec6553a0281b8bd2f9e4a1f35f60906</t>
         </is>
       </c>
       <c r="E955" s="2" t="inlineStr">
@@ -40757,14 +40757,14 @@
         <is>
           <t xml:space="preserve">Someone who was completing an interview using Massachusetts Defense for
 Eviction (MADE) sent you this link.
-Click [here](${interview_url()}) to keep working on the interview.
+[Keep working on the interview](${interview_url()}).
 </t>
         </is>
       </c>
       <c r="H955" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Yon moun ki t ap ranpli yon fòmilè entèvyou avèk Defans kont Degèpisman nan Massachusetts (MADE) te voye lyen sa a ba w.
-Klike [isit](${interview_url()}) pou w kontinye travay sou entèvyou a.
+[Kontinye travay sou entèvyou a](${interview_url()}).
 </t>
         </is>
       </c>
@@ -53003,6 +53003,207 @@
         </is>
       </c>
     </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>a2beb488f5408ec32ba0f33f24c6c5e1</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>ht</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>By hand</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>An pèsòn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>dfc27ef27b631b0e7114573a439c3180</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>ht</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>By email</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>Pa imèl</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1224" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>409b1ef3ad4fe98ad063fb3026c6b250</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>ht</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>By mail</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>Pa lapòs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1225" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>966afd80841437ca4adfcf8f54bfab2a</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>ht</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You must give a copy of the forms we are working on to your landlord or their 
+attorney. 
+% if case.hearing_date_assigned:
+They need to _get_ the forms no later than 
+**${format_date(case.answer_date)}**.
+% if answer_date_is_holiday:
+Because ${case.answer_date} is ${answer_date_holiday}, you can
+deliver it the next weekday after ${answer_date_holiday}.
+% endif
+% else:
+Give a copy to your landlord or their attorney as soon as you can.
+% endif
+Deliver it in person
+if you can. If your landlord has a lawyer, you can email it to the lawyer.
+If your landlord does not have a lawyer, ask them first before you email it. 
+% if format_date(case.answer_date) == format_date(today()):
+It's too late to mail the paperwork.
+% else:
+Only mail it if you know
+your landlord will get it on or before ${format_date(case.answer_date)}.
+% endif
+</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ou dwe bay pwopriyetè w la oswa avoka li yon kopi fòm nou ap travay sou yo. 
+% if case.hearing_date_assigned:
+Yo dwe _resevwa_ fòm yo pa pita pase 
+**${format_date(case.answer_date)}**.
+% if answer_date_is_holiday:
+Paske ${case.answer_date} se ${answer_date_holiday}, ou ka
+livre l nan pwochen jou ouvrab apre ${answer_date_holiday}.
+% endif
+% else:
+Bay pwopriyetè w la oswa avoka li yon kopi pi vit ou kapab.
+% endif
+Livre l an pèsòn
+si ou kapab. Si pwopriyetè w la gen yon avoka, ou ka voye l pa imèl bay avoka a.
+Si pwopriyetè w la pa gen avoka, mande l pèmisyon anvan ou voye l pa imèl. 
+% if format_date(case.answer_date) == format_date(today()):
+Li twò ta pou voye papye yo pa lapòs.
+% else:
+Voye l pa lapòs sèlman si w konnen
+pwopriyetè w la ap resevwa l nan dat ${format_date(case.answer_date)} oswa anvan.
+% endif
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
